--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -14495,9 +14495,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -14545,9 +14551,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1519</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -14595,9 +14607,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.119</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -14645,9 +14663,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1027</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -14695,9 +14719,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1945</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G434"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12146,6 +12146,33 @@
       <c r="G434" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>226.42</v>
+      </c>
+      <c r="C435" t="n">
+        <v>204.76</v>
+      </c>
+      <c r="D435" t="n">
+        <v>226.88</v>
+      </c>
+      <c r="E435" t="n">
+        <v>195.01</v>
+      </c>
+      <c r="F435" t="n">
+        <v>199.33</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17303,6 +17330,16 @@
       </c>
       <c r="B514" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -17465,28 +17502,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008717280658767595</v>
+        <v>-0.007236895508524134</v>
       </c>
       <c r="J2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002194356881491943</v>
+        <v>0.0001517305809448644</v>
       </c>
       <c r="M2" t="n">
-        <v>3.372141441610582</v>
+        <v>3.374134856778774</v>
       </c>
       <c r="N2" t="n">
-        <v>19.81257624425279</v>
+        <v>19.79424334367153</v>
       </c>
       <c r="O2" t="n">
-        <v>4.451132018290717</v>
+        <v>4.44907218908297</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1913274211855</v>
+        <v>223.1759772349264</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17537,28 +17574,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04381887311397719</v>
+        <v>0.04377462509378292</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004120834899696058</v>
+        <v>0.004131391610385338</v>
       </c>
       <c r="M3" t="n">
-        <v>4.107618414083136</v>
+        <v>4.098386533548361</v>
       </c>
       <c r="N3" t="n">
-        <v>26.55371597264037</v>
+        <v>26.49255670092828</v>
       </c>
       <c r="O3" t="n">
-        <v>5.153029785731921</v>
+        <v>5.147092062604697</v>
       </c>
       <c r="P3" t="n">
-        <v>203.706552114875</v>
+        <v>203.7070109247674</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17609,28 +17646,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2050469732163545</v>
+        <v>-0.2072468065019058</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03509077683553796</v>
+        <v>0.03594785537637013</v>
       </c>
       <c r="M4" t="n">
-        <v>6.420765164223621</v>
+        <v>6.415655455468857</v>
       </c>
       <c r="N4" t="n">
-        <v>66.15789301256973</v>
+        <v>66.06577835922843</v>
       </c>
       <c r="O4" t="n">
-        <v>8.133750242819712</v>
+        <v>8.128085774598373</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4253724856144</v>
+        <v>237.4481826648888</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17681,28 +17718,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2592168317625966</v>
+        <v>0.2564511061638466</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08853992623056195</v>
+        <v>0.08699788558123966</v>
       </c>
       <c r="M5" t="n">
-        <v>4.833116828021655</v>
+        <v>4.83635282458294</v>
       </c>
       <c r="N5" t="n">
-        <v>39.332292979451</v>
+        <v>39.33579661736409</v>
       </c>
       <c r="O5" t="n">
-        <v>6.271546298916321</v>
+        <v>6.271825620771363</v>
       </c>
       <c r="P5" t="n">
-        <v>194.575440415066</v>
+        <v>194.6042776962852</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17753,28 +17790,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1132831588464317</v>
+        <v>0.1095147403897172</v>
       </c>
       <c r="J6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02143158321467487</v>
+        <v>0.02004348324486471</v>
       </c>
       <c r="M6" t="n">
-        <v>4.236032958929299</v>
+        <v>4.240843362810572</v>
       </c>
       <c r="N6" t="n">
-        <v>33.69916421428137</v>
+        <v>33.79941269074153</v>
       </c>
       <c r="O6" t="n">
-        <v>5.805098122709156</v>
+        <v>5.813726231148276</v>
       </c>
       <c r="P6" t="n">
-        <v>205.1397626413371</v>
+        <v>205.1787858275414</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17812,7 +17849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G434"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33853,6 +33890,43 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:38+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-46.89937909098354,168.13883686363482</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-46.899815997794505,168.13971647542797</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-46.899834779921534,168.14041919871474</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-46.89957942083065,168.1414845442824</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-46.89907862807834,168.14223877296482</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12173,6 +12173,33 @@
       <c r="G435" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>221.95</v>
+      </c>
+      <c r="C436" t="n">
+        <v>202.48</v>
+      </c>
+      <c r="D436" t="n">
+        <v>221.16</v>
+      </c>
+      <c r="E436" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="F436" t="n">
+        <v>205.94</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17340,6 +17367,26 @@
       </c>
       <c r="B515" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -17502,28 +17549,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007236895508524134</v>
+        <v>-0.00768415352483265</v>
       </c>
       <c r="J2" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001517305809448644</v>
+        <v>0.000171849142661884</v>
       </c>
       <c r="M2" t="n">
-        <v>3.374134856778774</v>
+        <v>3.368196608761309</v>
       </c>
       <c r="N2" t="n">
-        <v>19.79424334367153</v>
+        <v>19.75117129241049</v>
       </c>
       <c r="O2" t="n">
-        <v>4.44907218908297</v>
+        <v>4.444228987395957</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1759772349264</v>
+        <v>223.1806585249834</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17574,28 +17621,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04377462509378292</v>
+        <v>0.0427365715697068</v>
       </c>
       <c r="J3" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004131391610385338</v>
+        <v>0.003955136867935138</v>
       </c>
       <c r="M3" t="n">
-        <v>4.098386533548361</v>
+        <v>4.094312260691927</v>
       </c>
       <c r="N3" t="n">
-        <v>26.49255670092828</v>
+        <v>26.44475450463891</v>
       </c>
       <c r="O3" t="n">
-        <v>5.147092062604697</v>
+        <v>5.142446354084689</v>
       </c>
       <c r="P3" t="n">
-        <v>203.7070109247674</v>
+        <v>203.7178758605845</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17646,28 +17693,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2072468065019058</v>
+        <v>-0.2119157565075537</v>
       </c>
       <c r="J4" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03594785537637013</v>
+        <v>0.0375498201852914</v>
       </c>
       <c r="M4" t="n">
-        <v>6.415655455468857</v>
+        <v>6.4211970491807</v>
       </c>
       <c r="N4" t="n">
-        <v>66.06577835922843</v>
+        <v>66.17892259187261</v>
       </c>
       <c r="O4" t="n">
-        <v>8.128085774598373</v>
+        <v>8.135042875847219</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4481826648888</v>
+        <v>237.4970508985278</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17718,28 +17765,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2564511061638466</v>
+        <v>0.252992982958565</v>
       </c>
       <c r="J5" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08699788558123966</v>
+        <v>0.08494774709998743</v>
       </c>
       <c r="M5" t="n">
-        <v>4.83635282458294</v>
+        <v>4.842828024440522</v>
       </c>
       <c r="N5" t="n">
-        <v>39.33579661736409</v>
+        <v>39.3890992317939</v>
       </c>
       <c r="O5" t="n">
-        <v>6.271825620771363</v>
+        <v>6.276073552133842</v>
       </c>
       <c r="P5" t="n">
-        <v>194.6042776962852</v>
+        <v>194.6406727053933</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17790,28 +17837,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1095147403897172</v>
+        <v>0.1085828345208685</v>
       </c>
       <c r="J6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02004348324486471</v>
+        <v>0.01979549023663874</v>
       </c>
       <c r="M6" t="n">
-        <v>4.240843362810572</v>
+        <v>4.234573015259552</v>
       </c>
       <c r="N6" t="n">
-        <v>33.79941269074153</v>
+        <v>33.73181481087132</v>
       </c>
       <c r="O6" t="n">
-        <v>5.813726231148276</v>
+        <v>5.807909676542097</v>
       </c>
       <c r="P6" t="n">
-        <v>205.1787858275414</v>
+        <v>205.188527866343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17849,7 +17896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33927,6 +33974,43 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:30+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-46.89941663578406,168.1388160764114</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-46.89983514825245,168.13970587276182</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-46.89987357094082,168.14046836996363</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-46.899589661003375,168.14149752495265</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-46.89903380860867,168.14218193950904</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12200,6 +12200,33 @@
       <c r="G436" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>221.91</v>
+      </c>
+      <c r="C437" t="n">
+        <v>203.48</v>
+      </c>
+      <c r="D437" t="n">
+        <v>221.27</v>
+      </c>
+      <c r="E437" t="n">
+        <v>194.53</v>
+      </c>
+      <c r="F437" t="n">
+        <v>205.66</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17387,6 +17414,16 @@
       </c>
       <c r="B517" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -17549,28 +17586,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00768415352483265</v>
+        <v>-0.008141638461319415</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000171849142661884</v>
+        <v>0.00019379882225945</v>
       </c>
       <c r="M2" t="n">
-        <v>3.368196608761309</v>
+        <v>3.362322884737722</v>
       </c>
       <c r="N2" t="n">
-        <v>19.75117129241049</v>
+        <v>19.70843448915101</v>
       </c>
       <c r="O2" t="n">
-        <v>4.444228987395957</v>
+        <v>4.439418260217324</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1806585249834</v>
+        <v>223.1854517518239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17621,28 +17658,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0427365715697068</v>
+        <v>0.04214166046894122</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003955136867935138</v>
+        <v>0.003863600684674173</v>
       </c>
       <c r="M3" t="n">
-        <v>4.094312260691927</v>
+        <v>4.087972971122752</v>
       </c>
       <c r="N3" t="n">
-        <v>26.44475450463891</v>
+        <v>26.38843727299151</v>
       </c>
       <c r="O3" t="n">
-        <v>5.142446354084689</v>
+        <v>5.136967711889136</v>
       </c>
       <c r="P3" t="n">
-        <v>203.7178758605845</v>
+        <v>203.7241089485586</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17693,28 +17730,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2119157565075537</v>
+        <v>-0.2164803228552859</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0375498201852914</v>
+        <v>0.03915228107309199</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4211970491807</v>
+        <v>6.426235522476656</v>
       </c>
       <c r="N4" t="n">
-        <v>66.17892259187261</v>
+        <v>66.28238954379935</v>
       </c>
       <c r="O4" t="n">
-        <v>8.135042875847219</v>
+        <v>8.141399728781247</v>
       </c>
       <c r="P4" t="n">
-        <v>237.4970508985278</v>
+        <v>237.5448754282303</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17765,28 +17802,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.252992982958565</v>
+        <v>0.2500208136129909</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08494774709998743</v>
+        <v>0.08327926519437434</v>
       </c>
       <c r="M5" t="n">
-        <v>4.842828024440522</v>
+        <v>4.84676682214707</v>
       </c>
       <c r="N5" t="n">
-        <v>39.3890992317939</v>
+        <v>39.40564396730242</v>
       </c>
       <c r="O5" t="n">
-        <v>6.276073552133842</v>
+        <v>6.277391493869283</v>
       </c>
       <c r="P5" t="n">
-        <v>194.6406727053933</v>
+        <v>194.6719851746695</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17837,28 +17874,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1085828345208685</v>
+        <v>0.107541954572248</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01979549023663874</v>
+        <v>0.01950685656312467</v>
       </c>
       <c r="M6" t="n">
-        <v>4.234573015259552</v>
+        <v>4.228735715715817</v>
       </c>
       <c r="N6" t="n">
-        <v>33.73181481087132</v>
+        <v>33.66729000990231</v>
       </c>
       <c r="O6" t="n">
-        <v>5.807909676542097</v>
+        <v>5.802352110127608</v>
       </c>
       <c r="P6" t="n">
-        <v>205.188527866343</v>
+        <v>205.1994203559751</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17896,7 +17933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34011,6 +34048,43 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-46.89941697175541,168.1388158903958</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-46.89982674892896,168.139710523055</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-46.89987282495985,168.14046742436204</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-46.89958267598502,168.14148867058765</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-46.89903570716463,168.14218434697577</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G437"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12225,6 +12225,33 @@
         <v>205.66</v>
       </c>
       <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>221.04</v>
+      </c>
+      <c r="C438" t="n">
+        <v>203.69</v>
+      </c>
+      <c r="D438" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="E438" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="F438" t="n">
+        <v>203.92</v>
+      </c>
+      <c r="G438" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12241,7 +12268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17424,6 +17451,16 @@
       </c>
       <c r="B518" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -17586,28 +17623,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008141638461319415</v>
+        <v>-0.008976407791638519</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00019379882225945</v>
+        <v>0.0002365857840901375</v>
       </c>
       <c r="M2" t="n">
-        <v>3.362322884737722</v>
+        <v>3.357976511198708</v>
       </c>
       <c r="N2" t="n">
-        <v>19.70843448915101</v>
+        <v>19.67179663950536</v>
       </c>
       <c r="O2" t="n">
-        <v>4.439418260217324</v>
+        <v>4.435289916060206</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1854517518239</v>
+        <v>223.1942434514593</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17658,28 +17695,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04214166046894122</v>
+        <v>0.0416393770548371</v>
       </c>
       <c r="J3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003863600684674173</v>
+        <v>0.003789836237246935</v>
       </c>
       <c r="M3" t="n">
-        <v>4.087972971122752</v>
+        <v>4.081162105245131</v>
       </c>
       <c r="N3" t="n">
-        <v>26.38843727299151</v>
+        <v>26.331115307442</v>
       </c>
       <c r="O3" t="n">
-        <v>5.136967711889136</v>
+        <v>5.131385320499914</v>
       </c>
       <c r="P3" t="n">
-        <v>203.7241089485586</v>
+        <v>203.7293989427501</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17730,28 +17767,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2164803228552859</v>
+        <v>-0.2193399225343966</v>
       </c>
       <c r="J4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03915228107309199</v>
+        <v>0.04027696723614571</v>
       </c>
       <c r="M4" t="n">
-        <v>6.426235522476656</v>
+        <v>6.423915812728302</v>
       </c>
       <c r="N4" t="n">
-        <v>66.28238954379935</v>
+        <v>66.23000852303466</v>
       </c>
       <c r="O4" t="n">
-        <v>8.141399728781247</v>
+        <v>8.138182138723282</v>
       </c>
       <c r="P4" t="n">
-        <v>237.5448754282303</v>
+        <v>237.5749924204858</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17802,28 +17839,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2500208136129909</v>
+        <v>0.2486796329446073</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08327926519437434</v>
+        <v>0.08278051237752193</v>
       </c>
       <c r="M5" t="n">
-        <v>4.84676682214707</v>
+        <v>4.842350061596324</v>
       </c>
       <c r="N5" t="n">
-        <v>39.40564396730242</v>
+        <v>39.33671126605256</v>
       </c>
       <c r="O5" t="n">
-        <v>6.277391493869283</v>
+        <v>6.271898537608254</v>
       </c>
       <c r="P5" t="n">
-        <v>194.6719851746695</v>
+        <v>194.6861881460465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17874,28 +17911,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.107541954572248</v>
+        <v>0.1057466161907388</v>
       </c>
       <c r="J6" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01950685656312467</v>
+        <v>0.01893919451456327</v>
       </c>
       <c r="M6" t="n">
-        <v>4.228735715715817</v>
+        <v>4.22569146043541</v>
       </c>
       <c r="N6" t="n">
-        <v>33.66729000990231</v>
+        <v>33.62916061996756</v>
       </c>
       <c r="O6" t="n">
-        <v>5.802352110127608</v>
+        <v>5.799065495402475</v>
       </c>
       <c r="P6" t="n">
-        <v>205.1994203559751</v>
+        <v>205.2183069200917</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17933,7 +17970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G437"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34085,6 +34122,43 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-46.89942427913209,168.13881184455673</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-46.89982498507099,168.13971149961637</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-46.899846579988825,168.1404341563949</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-46.8995572450879,168.14145643384117</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-46.89904750533276,168.14219930766555</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12252,6 +12252,87 @@
         <v>203.92</v>
       </c>
       <c r="G438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>220.69</v>
+      </c>
+      <c r="C439" t="n">
+        <v>205.22</v>
+      </c>
+      <c r="D439" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="E439" t="n">
+        <v>197.45</v>
+      </c>
+      <c r="F439" t="n">
+        <v>202.38</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>221.84</v>
+      </c>
+      <c r="C440" t="n">
+        <v>207.03</v>
+      </c>
+      <c r="D440" t="n">
+        <v>225.59</v>
+      </c>
+      <c r="E440" t="n">
+        <v>198.88</v>
+      </c>
+      <c r="F440" t="n">
+        <v>203.63</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>222.46</v>
+      </c>
+      <c r="C441" t="n">
+        <v>207.89</v>
+      </c>
+      <c r="D441" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="E441" t="n">
+        <v>198.58</v>
+      </c>
+      <c r="F441" t="n">
+        <v>202.38</v>
+      </c>
+      <c r="G441" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12268,7 +12349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17461,6 +17542,36 @@
       </c>
       <c r="B519" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -17623,28 +17734,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008976407791638519</v>
+        <v>-0.01062353567492041</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002365857840901375</v>
+        <v>0.000335816345366502</v>
       </c>
       <c r="M2" t="n">
-        <v>3.357976511198708</v>
+        <v>3.341702688820578</v>
       </c>
       <c r="N2" t="n">
-        <v>19.67179663950536</v>
+        <v>19.55240889397652</v>
       </c>
       <c r="O2" t="n">
-        <v>4.435289916060206</v>
+        <v>4.421810590015872</v>
       </c>
       <c r="P2" t="n">
-        <v>223.1942434514593</v>
+        <v>223.2116392067282</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17695,28 +17806,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0416393770548371</v>
+        <v>0.04402981006888844</v>
       </c>
       <c r="J3" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003789836237246935</v>
+        <v>0.004290537321165355</v>
       </c>
       <c r="M3" t="n">
-        <v>4.081162105245131</v>
+        <v>4.066331656325374</v>
       </c>
       <c r="N3" t="n">
-        <v>26.331115307442</v>
+        <v>26.18330006321213</v>
       </c>
       <c r="O3" t="n">
-        <v>5.131385320499914</v>
+        <v>5.116961995482488</v>
       </c>
       <c r="P3" t="n">
-        <v>203.7293989427501</v>
+        <v>203.704126801888</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17767,28 +17878,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2193399225343966</v>
+        <v>-0.2258951724337533</v>
       </c>
       <c r="J4" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04027696723614571</v>
+        <v>0.04306883371899439</v>
       </c>
       <c r="M4" t="n">
-        <v>6.423915812728302</v>
+        <v>6.408516034246385</v>
       </c>
       <c r="N4" t="n">
-        <v>66.23000852303466</v>
+        <v>65.98440361191849</v>
       </c>
       <c r="O4" t="n">
-        <v>8.138182138723282</v>
+        <v>8.123078456590118</v>
       </c>
       <c r="P4" t="n">
-        <v>237.5749924204858</v>
+        <v>237.6442405780224</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17839,28 +17950,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2486796329446073</v>
+        <v>0.2447551633429078</v>
       </c>
       <c r="J5" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08278051237752193</v>
+        <v>0.08132835451149223</v>
       </c>
       <c r="M5" t="n">
-        <v>4.842350061596324</v>
+        <v>4.829108770838378</v>
       </c>
       <c r="N5" t="n">
-        <v>39.33671126605256</v>
+        <v>39.13219178578229</v>
       </c>
       <c r="O5" t="n">
-        <v>6.271898537608254</v>
+        <v>6.255572858322592</v>
       </c>
       <c r="P5" t="n">
-        <v>194.6861881460465</v>
+        <v>194.7278768915038</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17911,28 +18022,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1057466161907388</v>
+        <v>0.09902180257305801</v>
       </c>
       <c r="J6" t="n">
+        <v>440</v>
+      </c>
+      <c r="K6" t="n">
         <v>437</v>
       </c>
-      <c r="K6" t="n">
-        <v>434</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01893919451456327</v>
+        <v>0.01678544656833825</v>
       </c>
       <c r="M6" t="n">
-        <v>4.22569146043541</v>
+        <v>4.221489279952856</v>
       </c>
       <c r="N6" t="n">
-        <v>33.62916061996756</v>
+        <v>33.58666631194908</v>
       </c>
       <c r="O6" t="n">
-        <v>5.799065495402475</v>
+        <v>5.795400444486048</v>
       </c>
       <c r="P6" t="n">
-        <v>205.2183069200917</v>
+        <v>205.2892827320833</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17970,7 +18081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34159,6 +34270,117 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-46.89942721888129,168.13881021691998</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-46.899812134105474,168.13971861456142</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-46.89985017426185,168.14043871247114</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-46.89956287379382,168.14146356890512</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-46.89905794738818,168.1422125487413</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-46.899417559705256,168.13881556486857</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-46.899796931328524,168.13972703158325</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-46.89984352824745,168.14043028802868</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-46.8995531761436,168.14145127596458</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-46.89904947169394,168.1422018011145</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-46.89941235214936,168.13881844810956</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-46.89978970790934,168.13973103082944</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-46.89981701200087,168.1403966762432</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-46.89955521061577,168.14145385490278</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-46.89905794738818,168.1422125487413</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G441"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12335,6 +12335,141 @@
       <c r="G441" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>217.86</v>
+      </c>
+      <c r="C442" t="n">
+        <v>207.79</v>
+      </c>
+      <c r="D442" t="n">
+        <v>233.19</v>
+      </c>
+      <c r="E442" t="n">
+        <v>198.39</v>
+      </c>
+      <c r="F442" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:03+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>215.75</v>
+      </c>
+      <c r="C443" t="n">
+        <v>205.12</v>
+      </c>
+      <c r="D443" t="n">
+        <v>229.51</v>
+      </c>
+      <c r="E443" t="n">
+        <v>196.85</v>
+      </c>
+      <c r="F443" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>215.32</v>
+      </c>
+      <c r="C444" t="n">
+        <v>204.31</v>
+      </c>
+      <c r="D444" t="n">
+        <v>227.86</v>
+      </c>
+      <c r="E444" t="n">
+        <v>195.57</v>
+      </c>
+      <c r="F444" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="C445" t="n">
+        <v>203.92</v>
+      </c>
+      <c r="D445" t="n">
+        <v>229.62</v>
+      </c>
+      <c r="E445" t="n">
+        <v>195.95</v>
+      </c>
+      <c r="F445" t="n">
+        <v>197.05</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="C446" t="n">
+        <v>203.92</v>
+      </c>
+      <c r="D446" t="n">
+        <v>229.62</v>
+      </c>
+      <c r="E446" t="n">
+        <v>195.95</v>
+      </c>
+      <c r="F446" t="n">
+        <v>197.33</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17572,6 +17707,56 @@
       </c>
       <c r="B522" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -17734,28 +17919,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01062353567492041</v>
+        <v>-0.02571935416842066</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000335816345366502</v>
+        <v>0.00195160926670146</v>
       </c>
       <c r="M2" t="n">
-        <v>3.341702688820578</v>
+        <v>3.365508030342783</v>
       </c>
       <c r="N2" t="n">
-        <v>19.55240889397652</v>
+        <v>19.92157948929714</v>
       </c>
       <c r="O2" t="n">
-        <v>4.421810590015872</v>
+        <v>4.463359663896373</v>
       </c>
       <c r="P2" t="n">
-        <v>223.2116392067282</v>
+        <v>223.37182473357</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17806,28 +17991,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04402981006888844</v>
+        <v>0.04428522316631268</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004290537321165355</v>
+        <v>0.004437239671330917</v>
       </c>
       <c r="M3" t="n">
-        <v>4.066331656325374</v>
+        <v>4.033350280083632</v>
       </c>
       <c r="N3" t="n">
-        <v>26.18330006321213</v>
+        <v>25.91303936235237</v>
       </c>
       <c r="O3" t="n">
-        <v>5.116961995482488</v>
+        <v>5.090485179464957</v>
       </c>
       <c r="P3" t="n">
-        <v>203.704126801888</v>
+        <v>203.7014459449786</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17878,28 +18063,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2258951724337533</v>
+        <v>-0.2292351503092374</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04306883371899439</v>
+        <v>0.04524309838048979</v>
       </c>
       <c r="M4" t="n">
-        <v>6.408516034246385</v>
+        <v>6.358634852935686</v>
       </c>
       <c r="N4" t="n">
-        <v>65.98440361191849</v>
+        <v>65.30520768343203</v>
       </c>
       <c r="O4" t="n">
-        <v>8.123078456590118</v>
+        <v>8.081163757988822</v>
       </c>
       <c r="P4" t="n">
-        <v>237.6442405780224</v>
+        <v>237.6796971209409</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17950,28 +18135,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2447551633429078</v>
+        <v>0.2347739662789016</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K5" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08132835451149223</v>
+        <v>0.07647506751173505</v>
       </c>
       <c r="M5" t="n">
-        <v>4.829108770838378</v>
+        <v>4.825442727907062</v>
       </c>
       <c r="N5" t="n">
-        <v>39.13219178578229</v>
+        <v>38.95072250382778</v>
       </c>
       <c r="O5" t="n">
-        <v>6.255572858322592</v>
+        <v>6.241051394102421</v>
       </c>
       <c r="P5" t="n">
-        <v>194.7278768915038</v>
+        <v>194.8343723418594</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18022,28 +18207,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09902180257305801</v>
+        <v>0.08182516267856557</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01678544656833825</v>
+        <v>0.01151538048938106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.221489279952856</v>
+        <v>4.239517628556033</v>
       </c>
       <c r="N6" t="n">
-        <v>33.58666631194908</v>
+        <v>34.00379485899447</v>
       </c>
       <c r="O6" t="n">
-        <v>5.795400444486048</v>
+        <v>5.831277292240052</v>
       </c>
       <c r="P6" t="n">
-        <v>205.2892827320833</v>
+        <v>205.4715818369098</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18081,7 +18266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G441"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34381,6 +34566,191 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-46.899450988852166,168.13879705630737</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-46.899790547841825,168.13973056580085</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-46.89979198770898,168.14036495568817</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-46.89955649911479,168.1414554882304</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-46.89906323622092,168.14221925526212</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:26:03+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-46.899468711337974,168.13878724396977</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-46.899812974037886,168.13971814953243</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-46.89981694418437,168.14039659027958</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-46.89956694273762,168.1414687267836</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-46.89906323622092,168.14221925526212</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-46.89947232302925,168.13878524429822</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-46.899819777490265,168.13971438279714</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-46.89982813390587,168.1404107742771</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-46.89957562315036,168.14147973026027</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-46.899068796275486,168.1422263057085</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-46.899477698569676,168.13878226804238</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-46.89982305322655,168.1397125691835</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-46.89981619820288,168.14039564467998</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-46.89957304615293,168.14147646360274</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-46.89909408773832,168.1422583766598</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-46.899477698569676,168.13878226804238</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-46.89982305322655,168.1397125691835</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-46.89981619820288,168.14039564467998</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-46.89957304615293,168.14147646360274</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-46.89909218918375,168.14225596918786</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
